--- a/Excel/ArtifactConfig.xlsx
+++ b/Excel/ArtifactConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="79">
   <si>
     <t>Id</t>
   </si>
@@ -47,7 +47,7 @@
     <t>MaxCount</t>
   </si>
   <si>
-    <t>DropRate</t>
+    <t>Quality</t>
   </si>
   <si>
     <t>Des</t>
@@ -146,13 +146,124 @@
     <t>财富契约</t>
   </si>
   <si>
-    <t>广告的金币经验收益+10%</t>
+    <t>广告的金币经验收益+10%，每10个额外+1经验丹</t>
   </si>
   <si>
     <t>天使之翼</t>
   </si>
   <si>
     <t>翅膀上限+1</t>
+  </si>
+  <si>
+    <t>分解机</t>
+  </si>
+  <si>
+    <t>分解精炼石+1</t>
+  </si>
+  <si>
+    <t>摄魂瓶</t>
+  </si>
+  <si>
+    <t>魂环碎片掉落+1</t>
+  </si>
+  <si>
+    <t>副本杀手</t>
+  </si>
+  <si>
+    <t>挑战装备副本，可以倍率+1</t>
+  </si>
+  <si>
+    <t>传世之源</t>
+  </si>
+  <si>
+    <t>传世等阶上限+1</t>
+  </si>
+  <si>
+    <t>神戒之源</t>
+  </si>
+  <si>
+    <t>神戒等级上限+1</t>
+  </si>
+  <si>
+    <t>传世契约</t>
+  </si>
+  <si>
+    <t>广告的传世劵收益+1</t>
+  </si>
+  <si>
+    <t>极·卖身契</t>
+  </si>
+  <si>
+    <t>超级矿工额外加1</t>
+  </si>
+  <si>
+    <t>极·圣者遗物</t>
+  </si>
+  <si>
+    <t>极·副本契约</t>
+  </si>
+  <si>
+    <t>广告的副本劵收益+3</t>
+  </si>
+  <si>
+    <t>极·BOSS契约</t>
+  </si>
+  <si>
+    <t>广告的BOSS劵收益+2</t>
+  </si>
+  <si>
+    <t>极·财富契约</t>
+  </si>
+  <si>
+    <t>广告的金币经验收益+100%，每1个额外+1经验丹</t>
+  </si>
+  <si>
+    <t>极·魔法书</t>
+  </si>
+  <si>
+    <t>所有技能上限提高15%</t>
+  </si>
+  <si>
+    <t>极·无限之魂</t>
+  </si>
+  <si>
+    <t>魂环等级上限+2</t>
+  </si>
+  <si>
+    <t>极·传世契约</t>
+  </si>
+  <si>
+    <t>广告的传世劵收益+2</t>
+  </si>
+  <si>
+    <t>极·万界图</t>
+  </si>
+  <si>
+    <t>所有图鉴基础上限提高1级</t>
+  </si>
+  <si>
+    <t>极·金蛟剪</t>
+  </si>
+  <si>
+    <t>时装等级上限10%</t>
+  </si>
+  <si>
+    <t>极·炼体证明</t>
+  </si>
+  <si>
+    <t>炼体秘境的产出提高5%</t>
+  </si>
+  <si>
+    <t>极·炼气证明</t>
+  </si>
+  <si>
+    <t>炼气秘境的产出提高5%</t>
+  </si>
+  <si>
+    <t>极·炼神证明</t>
+  </si>
+  <si>
+    <t>炼神秘境的产出提高5%</t>
   </si>
 </sst>
 </file>
@@ -338,12 +449,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -668,7 +785,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,16 +809,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -710,95 +827,97 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1118,7 +1237,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:J21"/>
+  <dimension ref="C3:J42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1130,80 +1249,80 @@
   </cols>
   <sheetData>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="I3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="I4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:10">
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1211,7 +1330,7 @@
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="4">
         <v>180001</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -1227,7 +1346,7 @@
         <v>4</v>
       </c>
       <c r="I6" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>11</v>
@@ -1237,7 +1356,7 @@
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="4">
         <v>180002</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -1253,7 +1372,7 @@
         <v>4</v>
       </c>
       <c r="I7" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>13</v>
@@ -1263,7 +1382,7 @@
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="4">
         <v>180003</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1279,7 +1398,7 @@
         <v>780</v>
       </c>
       <c r="I8" s="1">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>15</v>
@@ -1289,7 +1408,7 @@
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="4">
         <v>180004</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1305,7 +1424,7 @@
         <v>8</v>
       </c>
       <c r="I9" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>17</v>
@@ -1315,7 +1434,7 @@
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>180005</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1331,35 +1450,35 @@
         <v>10</v>
       </c>
       <c r="I10" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:10">
-      <c r="C11" s="1">
-        <v>6</v>
-      </c>
-      <c r="D11" s="3">
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C11" s="2">
+        <v>6</v>
+      </c>
+      <c r="D11" s="5">
         <v>180006</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="1">
-        <v>6</v>
-      </c>
-      <c r="G11" s="1">
+      <c r="F11" s="2">
+        <v>6</v>
+      </c>
+      <c r="G11" s="2">
         <v>10</v>
       </c>
-      <c r="H11" s="1">
-        <v>20</v>
-      </c>
-      <c r="I11" s="1">
-        <v>20</v>
-      </c>
-      <c r="J11" s="1" t="s">
+      <c r="H11" s="2">
+        <v>800</v>
+      </c>
+      <c r="I11" s="2">
+        <v>6</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1367,7 +1486,7 @@
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="4">
         <v>180007</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1383,7 +1502,7 @@
         <v>2</v>
       </c>
       <c r="I12" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>23</v>
@@ -1393,7 +1512,7 @@
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="4">
         <v>180008</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1409,7 +1528,7 @@
         <v>20</v>
       </c>
       <c r="I13" s="1">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>25</v>
@@ -1419,7 +1538,7 @@
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="4">
         <v>180009</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -1435,7 +1554,7 @@
         <v>4</v>
       </c>
       <c r="I14" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>27</v>
@@ -1445,7 +1564,7 @@
       <c r="C15" s="1">
         <v>10</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="4">
         <v>180010</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1461,139 +1580,139 @@
         <v>10</v>
       </c>
       <c r="I15" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:10">
-      <c r="C16" s="1">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C16" s="2">
         <v>11</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="5">
         <v>180011</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2">
         <v>11</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="2">
         <v>1000</v>
       </c>
-      <c r="H16" s="1">
-        <v>50</v>
-      </c>
-      <c r="I16" s="1">
+      <c r="H16" s="2">
+        <v>1200</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C17" s="2">
+        <v>12</v>
+      </c>
+      <c r="D17" s="5">
+        <v>180012</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="2">
+        <v>12</v>
+      </c>
+      <c r="G17" s="2">
+        <v>5</v>
+      </c>
+      <c r="H17" s="2">
         <v>100</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:10">
-      <c r="C17" s="1">
-        <v>12</v>
-      </c>
-      <c r="D17" s="3">
-        <v>180012</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F17" s="1">
-        <v>12</v>
-      </c>
-      <c r="G17" s="1">
-        <v>5</v>
-      </c>
-      <c r="H17" s="1">
-        <v>30</v>
-      </c>
-      <c r="I17" s="1">
-        <v>100</v>
-      </c>
-      <c r="J17" s="1" t="s">
+      <c r="I17" s="2">
+        <v>6</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="3:10">
-      <c r="C18" s="1">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C18" s="2">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="5">
         <v>180013</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="2">
         <v>13</v>
       </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="2">
+        <v>1600</v>
+      </c>
+      <c r="I18" s="2">
+        <v>6</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C19" s="2">
+        <v>14</v>
+      </c>
+      <c r="D19" s="5">
+        <v>180014</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="2">
+        <v>14</v>
+      </c>
+      <c r="G19" s="2">
         <v>10</v>
       </c>
-      <c r="I18" s="1">
+      <c r="H19" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I19" s="2">
+        <v>6</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C20" s="2">
+        <v>15</v>
+      </c>
+      <c r="D20" s="5">
+        <v>180015</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="2">
+        <v>15</v>
+      </c>
+      <c r="G20" s="2">
         <v>10</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:10">
-      <c r="C19" s="1">
-        <v>14</v>
-      </c>
-      <c r="D19" s="3">
-        <v>180014</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="1">
-        <v>14</v>
-      </c>
-      <c r="G19" s="1">
-        <v>10</v>
-      </c>
-      <c r="H19" s="1">
-        <v>100</v>
-      </c>
-      <c r="I19" s="1">
-        <v>100</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:10">
-      <c r="C20" s="1">
-        <v>15</v>
-      </c>
-      <c r="D20" s="3">
-        <v>180015</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="1">
-        <v>15</v>
-      </c>
-      <c r="G20" s="1">
-        <v>10</v>
-      </c>
-      <c r="H20" s="1">
-        <v>100</v>
-      </c>
-      <c r="I20" s="1">
-        <v>100</v>
-      </c>
-      <c r="J20" s="1" t="s">
+      <c r="H20" s="2">
+        <v>1200</v>
+      </c>
+      <c r="I20" s="2">
+        <v>6</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1601,7 +1720,7 @@
       <c r="C21" s="1">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="4">
         <v>180016</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1617,15 +1736,509 @@
         <v>1</v>
       </c>
       <c r="I21" s="1">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>41</v>
       </c>
     </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C22" s="2">
+        <v>17</v>
+      </c>
+      <c r="D22" s="5">
+        <v>180017</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="2">
+        <v>17</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I22" s="2">
+        <v>6</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C23" s="2">
+        <v>18</v>
+      </c>
+      <c r="D23" s="5">
+        <v>180018</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" s="2">
+        <v>18</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1</v>
+      </c>
+      <c r="H23" s="2">
+        <v>300</v>
+      </c>
+      <c r="I23" s="2">
+        <v>6</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:10">
+      <c r="C24" s="1">
+        <v>19</v>
+      </c>
+      <c r="D24" s="4">
+        <v>180019</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F24" s="1">
+        <v>19</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1</v>
+      </c>
+      <c r="H24" s="1">
+        <v>5</v>
+      </c>
+      <c r="I24" s="1">
+        <v>6</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C25" s="2">
+        <v>20</v>
+      </c>
+      <c r="D25" s="5">
+        <v>180020</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="2">
+        <v>20</v>
+      </c>
+      <c r="G25" s="2">
+        <v>1</v>
+      </c>
+      <c r="H25" s="2">
+        <v>350</v>
+      </c>
+      <c r="I25" s="2">
+        <v>6</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C26" s="2">
+        <v>21</v>
+      </c>
+      <c r="D26" s="5">
+        <v>180021</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26" s="2">
+        <v>21</v>
+      </c>
+      <c r="G26" s="2">
+        <v>1</v>
+      </c>
+      <c r="H26" s="2">
+        <v>250</v>
+      </c>
+      <c r="I26" s="2">
+        <v>6</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:10">
+      <c r="C27" s="2">
+        <v>22</v>
+      </c>
+      <c r="D27" s="5">
+        <v>180022</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="2">
+        <v>22</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2">
+        <v>4</v>
+      </c>
+      <c r="I27" s="2">
+        <v>6</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:10">
+      <c r="C30" s="1">
+        <v>30</v>
+      </c>
+      <c r="D30" s="4">
+        <v>180030</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" s="1">
+        <v>30</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1</v>
+      </c>
+      <c r="H30" s="1">
+        <v>80</v>
+      </c>
+      <c r="I30" s="1">
+        <v>7</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:10">
+      <c r="C31" s="1">
+        <v>31</v>
+      </c>
+      <c r="D31" s="4">
+        <v>180031</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1">
+        <v>1</v>
+      </c>
+      <c r="H31" s="1">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1">
+        <v>7</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:10">
+      <c r="C32" s="1">
+        <v>32</v>
+      </c>
+      <c r="D32" s="4">
+        <v>180032</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F32" s="1">
+        <v>4</v>
+      </c>
+      <c r="G32" s="1">
+        <v>3</v>
+      </c>
+      <c r="H32" s="1">
+        <v>16</v>
+      </c>
+      <c r="I32" s="1">
+        <v>7</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:10">
+      <c r="C33" s="1">
+        <v>33</v>
+      </c>
+      <c r="D33" s="4">
+        <v>180033</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" s="1">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1">
+        <v>2</v>
+      </c>
+      <c r="H33" s="1">
+        <v>8</v>
+      </c>
+      <c r="I33" s="1">
+        <v>7</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:10">
+      <c r="C34" s="1">
+        <v>34</v>
+      </c>
+      <c r="D34" s="4">
+        <v>180034</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" s="1">
+        <v>15</v>
+      </c>
+      <c r="G34" s="1">
+        <v>100</v>
+      </c>
+      <c r="H34" s="1">
+        <v>40</v>
+      </c>
+      <c r="I34" s="1">
+        <v>7</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:10">
+      <c r="C35" s="1">
+        <v>35</v>
+      </c>
+      <c r="D35" s="4">
+        <v>180035</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F35" s="1">
+        <v>8</v>
+      </c>
+      <c r="G35" s="1">
+        <v>15</v>
+      </c>
+      <c r="H35" s="1">
+        <v>10</v>
+      </c>
+      <c r="I35" s="1">
+        <v>7</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:10">
+      <c r="C36" s="1">
+        <v>36</v>
+      </c>
+      <c r="D36" s="4">
+        <v>180036</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F36" s="1">
+        <v>10</v>
+      </c>
+      <c r="G36" s="1">
+        <v>2</v>
+      </c>
+      <c r="H36" s="1">
+        <v>30</v>
+      </c>
+      <c r="I36" s="1">
+        <v>7</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:10">
+      <c r="C37" s="1">
+        <v>37</v>
+      </c>
+      <c r="D37" s="4">
+        <v>180037</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F37" s="1">
+        <v>22</v>
+      </c>
+      <c r="G37" s="1">
+        <v>2</v>
+      </c>
+      <c r="H37" s="1">
+        <v>4</v>
+      </c>
+      <c r="I37" s="1">
+        <v>7</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:10">
+      <c r="C38" s="1">
+        <v>38</v>
+      </c>
+      <c r="D38" s="4">
+        <v>180038</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" s="2">
+        <v>23</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1</v>
+      </c>
+      <c r="H38" s="1">
+        <v>40</v>
+      </c>
+      <c r="I38" s="1">
+        <v>7</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:10">
+      <c r="C39" s="1">
+        <v>39</v>
+      </c>
+      <c r="D39" s="4">
+        <v>180039</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F39" s="1">
+        <v>39</v>
+      </c>
+      <c r="G39" s="1">
+        <v>10</v>
+      </c>
+      <c r="H39" s="1">
+        <v>50</v>
+      </c>
+      <c r="I39" s="1">
+        <v>7</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:10">
+      <c r="C40" s="1">
+        <v>40</v>
+      </c>
+      <c r="D40" s="4">
+        <v>180040</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F40" s="1">
+        <v>40</v>
+      </c>
+      <c r="G40" s="1">
+        <v>5</v>
+      </c>
+      <c r="H40" s="1">
+        <v>20</v>
+      </c>
+      <c r="I40" s="1">
+        <v>7</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:10">
+      <c r="C41" s="1">
+        <v>41</v>
+      </c>
+      <c r="D41" s="4">
+        <v>180041</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="F41" s="1">
+        <v>41</v>
+      </c>
+      <c r="G41" s="1">
+        <v>5</v>
+      </c>
+      <c r="H41" s="1">
+        <v>20</v>
+      </c>
+      <c r="I41" s="1">
+        <v>7</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:10">
+      <c r="C42" s="1">
+        <v>42</v>
+      </c>
+      <c r="D42" s="4">
+        <v>180042</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F42" s="1">
+        <v>42</v>
+      </c>
+      <c r="G42" s="1">
+        <v>5</v>
+      </c>
+      <c r="H42" s="1">
+        <v>20</v>
+      </c>
+      <c r="I42" s="1">
+        <v>7</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3 D3 E3 F3 D4 F4 D5 F5 C4:C5 E4:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
